--- a/reports/pdf_change_20261014.xlsx
+++ b/reports/pdf_change_20261014.xlsx
@@ -574,7 +574,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 5,163억   ·   현금 72억(1.4%)      당일 2026-10-14  vs  전영업일 2026-10-13      매수 1종목  /  매도 9종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 5,127억      당일 2026-10-14  vs  전영업일 2026-10-13      매수 1종목  /  매도 9종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -670,7 +670,7 @@
         <v>247</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>1537200118</v>
+        <v>1537200025</v>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
         <v>-59</v>
       </c>
       <c r="I6" s="15" t="n">
-        <v>-1031978225</v>
+        <v>-1031978162</v>
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
         <v>-51</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>-966344271</v>
+        <v>-966344213</v>
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
@@ -747,7 +747,7 @@
         <v>-34</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>-1012505068</v>
+        <v>-1012505007</v>
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>-27</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-1008739266</v>
+        <v>-1008739205</v>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>-23</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-959585649</v>
+        <v>-959585590</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
@@ -831,7 +831,7 @@
         <v>-21</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>-1048874781</v>
+        <v>-1048874718</v>
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
@@ -859,7 +859,7 @@
         <v>-6</v>
       </c>
       <c r="I12" s="15" t="n">
-        <v>-894873325</v>
+        <v>-894873271</v>
       </c>
       <c r="J12" s="16" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>-5</v>
       </c>
       <c r="I13" s="15" t="n">
-        <v>-440995160</v>
+        <v>-440995134</v>
       </c>
       <c r="J13" s="16" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>-4</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>-1038568377</v>
+        <v>-1038568314</v>
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
     <row r="16" ht="19" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,174억   ·   현금 26억(0.8%)      당일 2026-10-14  vs  전영업일 2026-10-13      매수 0종목  /  매도 0종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,017억      당일 2026-10-14  vs  전영업일 2026-10-13      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B16" s="4" t="n"/>
@@ -955,7 +955,7 @@
     <row r="19" ht="19" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,664억   ·   현금 38억(1.4%)      당일 2026-10-14  vs  전영업일 2026-10-13      매수 3종목  /  매도 6종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,650억      당일 2026-10-14  vs  전영업일 2026-10-13      매수 3종목  /  매도 6종목</t>
         </is>
       </c>
       <c r="B19" s="4" t="n"/>
@@ -1051,7 +1051,7 @@
         <v>36</v>
       </c>
       <c r="C22" s="11" t="n">
-        <v>1894160683</v>
+        <v>1891295542</v>
       </c>
       <c r="D22" s="12" t="inlineStr">
         <is>
@@ -1072,7 +1072,7 @@
         <v>-150</v>
       </c>
       <c r="I22" s="15" t="n">
-        <v>-4174212979</v>
+        <v>-4167898990</v>
       </c>
       <c r="J22" s="16" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>25</v>
       </c>
       <c r="C23" s="11" t="n">
-        <v>3569398272</v>
+        <v>3563999136</v>
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>-39</v>
       </c>
       <c r="I23" s="15" t="n">
-        <v>-2345887864</v>
+        <v>-2342339432</v>
       </c>
       <c r="J23" s="16" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>21</v>
       </c>
       <c r="C24" s="11" t="n">
-        <v>3636820239</v>
+        <v>3631319120</v>
       </c>
       <c r="D24" s="12" t="inlineStr">
         <is>
@@ -1160,7 +1160,7 @@
         <v>-30</v>
       </c>
       <c r="I24" s="15" t="n">
-        <v>-478894268</v>
+        <v>-478169884</v>
       </c>
       <c r="J24" s="16" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>-25</v>
       </c>
       <c r="I25" s="15" t="n">
-        <v>-576722221</v>
+        <v>-575849860</v>
       </c>
       <c r="J25" s="16" t="inlineStr">
         <is>
@@ -1216,7 +1216,7 @@
         <v>-20</v>
       </c>
       <c r="I26" s="15" t="n">
-        <v>-830215598</v>
+        <v>-828959799</v>
       </c>
       <c r="J26" s="16" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>-6</v>
       </c>
       <c r="I27" s="15" t="n">
-        <v>-1082717476</v>
+        <v>-1081079738</v>
       </c>
       <c r="J27" s="16" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
     <row r="29" ht="19" customHeight="1">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,028억   ·   현금 6억(0.3%)      당일 2026-10-14  vs  전영업일 2026-10-13      매수 6종목  /  매도 6종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 1,933억      당일 2026-10-14  vs  전영업일 2026-10-13      매수 6종목  /  매도 6종목</t>
         </is>
       </c>
       <c r="B29" s="4" t="n"/>
@@ -1356,7 +1356,7 @@
         <v>125</v>
       </c>
       <c r="C32" s="11" t="n">
-        <v>2132830248</v>
+        <v>2132831696</v>
       </c>
       <c r="D32" s="12" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>-126</v>
       </c>
       <c r="I32" s="15" t="n">
-        <v>-1599751948</v>
+        <v>-1599753034</v>
       </c>
       <c r="J32" s="16" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
         <v>108</v>
       </c>
       <c r="C33" s="11" t="n">
-        <v>928621364</v>
+        <v>928621994</v>
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
@@ -1421,7 +1421,7 @@
         <v>-108</v>
       </c>
       <c r="I33" s="15" t="n">
-        <v>-965848946</v>
+        <v>-965849602</v>
       </c>
       <c r="J33" s="16" t="inlineStr">
         <is>
@@ -1444,7 +1444,7 @@
         <v>59</v>
       </c>
       <c r="C34" s="11" t="n">
-        <v>994267533</v>
+        <v>994268208</v>
       </c>
       <c r="D34" s="12" t="inlineStr">
         <is>
@@ -1465,7 +1465,7 @@
         <v>-102</v>
       </c>
       <c r="I34" s="15" t="n">
-        <v>-3555004329</v>
+        <v>-3555006743</v>
       </c>
       <c r="J34" s="16" t="inlineStr">
         <is>
@@ -1488,7 +1488,7 @@
         <v>58</v>
       </c>
       <c r="C35" s="11" t="n">
-        <v>966308546</v>
+        <v>966309202</v>
       </c>
       <c r="D35" s="12" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         <v>-62</v>
       </c>
       <c r="I35" s="15" t="n">
-        <v>-996144232</v>
+        <v>-996144908</v>
       </c>
       <c r="J35" s="16" t="inlineStr">
         <is>
@@ -1532,7 +1532,7 @@
         <v>37</v>
       </c>
       <c r="C36" s="11" t="n">
-        <v>2546527503</v>
+        <v>2546529232</v>
       </c>
       <c r="D36" s="12" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         <v>-11</v>
       </c>
       <c r="I36" s="15" t="n">
-        <v>-1908488103</v>
+        <v>-1908489399</v>
       </c>
       <c r="J36" s="16" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
         <v>25</v>
       </c>
       <c r="C37" s="11" t="n">
-        <v>2149586490</v>
+        <v>2149587949</v>
       </c>
       <c r="D37" s="12" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
         <v>-3</v>
       </c>
       <c r="I37" s="15" t="n">
-        <v>-26771687</v>
+        <v>-26771706</v>
       </c>
       <c r="J37" s="16" t="inlineStr">
         <is>

--- a/reports/pdf_change_20261014.xlsx
+++ b/reports/pdf_change_20261014.xlsx
@@ -541,7 +541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K43"/>
+  <dimension ref="A1:K44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -567,7 +567,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>캡처 4/7  ·  대기: PLUS, RISE, TIGER</t>
+          <t>캡처 5/7  ·  대기: RISE, TIGER</t>
         </is>
       </c>
     </row>
@@ -1611,58 +1611,65 @@
       </c>
     </row>
     <row r="39" ht="19" customHeight="1">
-      <c r="A39" s="19" t="inlineStr">
-        <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B39" s="20" t="n"/>
-      <c r="C39" s="20" t="n"/>
-      <c r="D39" s="20" t="n"/>
-      <c r="E39" s="20" t="n"/>
-      <c r="F39" s="20" t="n"/>
-      <c r="G39" s="20" t="n"/>
-      <c r="H39" s="20" t="n"/>
-      <c r="I39" s="20" t="n"/>
-      <c r="J39" s="20" t="n"/>
-      <c r="K39" s="20" t="n"/>
-    </row>
-    <row r="41" ht="19" customHeight="1">
-      <c r="A41" s="19" t="inlineStr">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 306억   ·   현금 4억(1.1%)      당일 2026-10-14  vs  전영업일 2026-10-13      매수 0종목  /  매도 0종목</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="n"/>
+      <c r="C39" s="4" t="n"/>
+      <c r="D39" s="4" t="n"/>
+      <c r="E39" s="4" t="n"/>
+      <c r="F39" s="4" t="n"/>
+      <c r="G39" s="4" t="n"/>
+      <c r="H39" s="4" t="n"/>
+      <c r="I39" s="4" t="n"/>
+      <c r="J39" s="4" t="n"/>
+      <c r="K39" s="4" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="18" t="inlineStr">
+        <is>
+          <t>변화 없음 (구성종목 동일)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="19" customHeight="1">
+      <c r="A42" s="19" t="inlineStr">
         <is>
           <t>■ RISE 바이오TOP10액티브  (KB)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
         </is>
       </c>
-      <c r="B41" s="20" t="n"/>
-      <c r="C41" s="20" t="n"/>
-      <c r="D41" s="20" t="n"/>
-      <c r="E41" s="20" t="n"/>
-      <c r="F41" s="20" t="n"/>
-      <c r="G41" s="20" t="n"/>
-      <c r="H41" s="20" t="n"/>
-      <c r="I41" s="20" t="n"/>
-      <c r="J41" s="20" t="n"/>
-      <c r="K41" s="20" t="n"/>
-    </row>
-    <row r="43" ht="19" customHeight="1">
-      <c r="A43" s="19" t="inlineStr">
+      <c r="B42" s="20" t="n"/>
+      <c r="C42" s="20" t="n"/>
+      <c r="D42" s="20" t="n"/>
+      <c r="E42" s="20" t="n"/>
+      <c r="F42" s="20" t="n"/>
+      <c r="G42" s="20" t="n"/>
+      <c r="H42" s="20" t="n"/>
+      <c r="I42" s="20" t="n"/>
+      <c r="J42" s="20" t="n"/>
+      <c r="K42" s="20" t="n"/>
+    </row>
+    <row r="44" ht="19" customHeight="1">
+      <c r="A44" s="19" t="inlineStr">
         <is>
           <t>■ TIGER 기술이전바이오액티브  (미래에셋)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
         </is>
       </c>
-      <c r="B43" s="20" t="n"/>
-      <c r="C43" s="20" t="n"/>
-      <c r="D43" s="20" t="n"/>
-      <c r="E43" s="20" t="n"/>
-      <c r="F43" s="20" t="n"/>
-      <c r="G43" s="20" t="n"/>
-      <c r="H43" s="20" t="n"/>
-      <c r="I43" s="20" t="n"/>
-      <c r="J43" s="20" t="n"/>
-      <c r="K43" s="20" t="n"/>
+      <c r="B44" s="20" t="n"/>
+      <c r="C44" s="20" t="n"/>
+      <c r="D44" s="20" t="n"/>
+      <c r="E44" s="20" t="n"/>
+      <c r="F44" s="20" t="n"/>
+      <c r="G44" s="20" t="n"/>
+      <c r="H44" s="20" t="n"/>
+      <c r="I44" s="20" t="n"/>
+      <c r="J44" s="20" t="n"/>
+      <c r="K44" s="20" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="17">
     <mergeCell ref="A30:E30"/>
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="G30:K30"/>
@@ -1671,11 +1678,12 @@
     <mergeCell ref="G20:K20"/>
     <mergeCell ref="A39:K39"/>
     <mergeCell ref="A29:K29"/>
-    <mergeCell ref="A43:K43"/>
-    <mergeCell ref="A41:K41"/>
     <mergeCell ref="A2:K2"/>
     <mergeCell ref="A16:K16"/>
     <mergeCell ref="A19:K19"/>
+    <mergeCell ref="A42:K42"/>
+    <mergeCell ref="A40:K40"/>
+    <mergeCell ref="A44:K44"/>
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="A17:K17"/>
     <mergeCell ref="G4:K4"/>

--- a/reports/pdf_change_20261014.xlsx
+++ b/reports/pdf_change_20261014.xlsx
@@ -1613,7 +1613,7 @@
     <row r="39" ht="19" customHeight="1">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 306억   ·   현금 4억(1.1%)      당일 2026-10-14  vs  전영업일 2026-10-13      매수 0종목  /  매도 0종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 306억      당일 2026-10-14  vs  전영업일 2026-10-13      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B39" s="4" t="n"/>
